--- a/bin/rfcs_resolutions_source.xlsx
+++ b/bin/rfcs_resolutions_source.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\IQA\iqa-report\bin\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\IQA\iqa\bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B7A30D5-6E0B-4E3F-B9D1-52699AE930F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EFFB255-A4FA-40CF-9C14-E321133F1FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F0251EA6-13F4-4529-A267-04DB69F86D66}"/>
+    <workbookView xWindow="1965" yWindow="2490" windowWidth="24960" windowHeight="11430" xr2:uid="{F0251EA6-13F4-4529-A267-04DB69F86D66}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,6 +27,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Year</t>
   </si>
@@ -112,13 +114,16 @@
   </si>
   <si>
     <t>Full Correction</t>
+  </si>
+  <si>
+    <t>FY24</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,6 +136,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -150,15 +161,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal_Sheet1" xfId="1" xr:uid="{0F731DA4-C51E-4844-91B4-86C46526E612}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -470,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AC84BCA-3EC8-40FB-A17D-2A5E56607C24}">
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" style="1" customWidth="1"/>
@@ -921,6 +935,26 @@
         <v>2</v>
       </c>
     </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="2">
+        <v>1</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2">
+        <v>5</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/bin/rfcs_resolutions_source.xlsx
+++ b/bin/rfcs_resolutions_source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\IQA\iqa\bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EFFB255-A4FA-40CF-9C14-E321133F1FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AC23E41-88CB-4419-A7CD-063B34B7B4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1965" yWindow="2490" windowWidth="24960" windowHeight="11430" xr2:uid="{F0251EA6-13F4-4529-A267-04DB69F86D66}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F0251EA6-13F4-4529-A267-04DB69F86D66}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Year</t>
   </si>
@@ -117,6 +120,9 @@
   </si>
   <si>
     <t>FY24</t>
+  </si>
+  <si>
+    <t>FY25</t>
   </si>
 </sst>
 </file>
@@ -484,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AC84BCA-3EC8-40FB-A17D-2A5E56607C24}">
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" style="1" customWidth="1"/>
@@ -955,6 +961,26 @@
         <v>2</v>
       </c>
     </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="1">
+        <v>6</v>
+      </c>
+      <c r="C23" s="1">
+        <v>1</v>
+      </c>
+      <c r="D23" s="1">
+        <v>8</v>
+      </c>
+      <c r="E23" s="1">
+        <v>5</v>
+      </c>
+      <c r="F23" s="1">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/bin/rfcs_resolutions_source.xlsx
+++ b/bin/rfcs_resolutions_source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\IQA\iqa\bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AC23E41-88CB-4419-A7CD-063B34B7B4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{809FCB3E-6E29-471A-9612-FBAE97106E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F0251EA6-13F4-4529-A267-04DB69F86D66}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Year</t>
   </si>
@@ -95,21 +95,6 @@
     <t>FY18</t>
   </si>
   <si>
-    <t>FY19</t>
-  </si>
-  <si>
-    <t>FY20</t>
-  </si>
-  <si>
-    <t>FY21</t>
-  </si>
-  <si>
-    <t>FY22</t>
-  </si>
-  <si>
-    <t>FY23</t>
-  </si>
-  <si>
     <t>No Correction</t>
   </si>
   <si>
@@ -117,12 +102,6 @@
   </si>
   <si>
     <t>Full Correction</t>
-  </si>
-  <si>
-    <t>FY24</t>
-  </si>
-  <si>
-    <t>FY25</t>
   </si>
 </sst>
 </file>
@@ -490,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AC84BCA-3EC8-40FB-A17D-2A5E56607C24}">
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" style="1" customWidth="1"/>
@@ -506,13 +485,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -523,7 +502,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1">
         <v>10</v>
@@ -841,145 +820,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="1">
-        <v>3</v>
-      </c>
-      <c r="C17" s="1">
-        <v>2</v>
-      </c>
-      <c r="D17" s="1">
-        <v>15</v>
-      </c>
-      <c r="E17" s="1">
-        <v>2</v>
-      </c>
-      <c r="F17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="1">
-        <v>3</v>
-      </c>
-      <c r="C18" s="1">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1">
-        <v>8</v>
-      </c>
-      <c r="E18" s="1">
-        <v>0</v>
-      </c>
-      <c r="F18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="1">
-        <v>2</v>
-      </c>
-      <c r="C19" s="1">
-        <v>0</v>
-      </c>
-      <c r="D19" s="1">
-        <v>11</v>
-      </c>
-      <c r="E19" s="1">
-        <v>0</v>
-      </c>
-      <c r="F19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="1">
-        <v>4</v>
-      </c>
-      <c r="C20" s="1">
-        <v>1</v>
-      </c>
-      <c r="D20" s="1">
-        <v>6</v>
-      </c>
-      <c r="E20" s="1">
-        <v>0</v>
-      </c>
-      <c r="F20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="1">
-        <v>11</v>
-      </c>
-      <c r="C21" s="1">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1">
-        <v>7</v>
-      </c>
-      <c r="E21" s="1">
-        <v>0</v>
-      </c>
-      <c r="F21" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="2">
-        <v>1</v>
-      </c>
-      <c r="C22" s="2">
-        <v>1</v>
-      </c>
-      <c r="D22" s="2">
-        <v>5</v>
-      </c>
-      <c r="E22" s="2">
-        <v>1</v>
-      </c>
-      <c r="F22" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="1">
-        <v>6</v>
-      </c>
-      <c r="C23" s="1">
-        <v>1</v>
-      </c>
-      <c r="D23" s="1">
-        <v>8</v>
-      </c>
-      <c r="E23" s="1">
-        <v>5</v>
-      </c>
-      <c r="F23" s="1">
-        <v>10</v>
-      </c>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
